--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>24h Change</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Volume(24h)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -444,12 +449,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.7009</t>
+          <t>$0.6968</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47.13%</t>
+          <t>48.06%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>$285,903,398</t>
         </is>
       </c>
     </row>
@@ -464,12 +474,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.301</t>
+          <t>$0.3011</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>$217,787,632</t>
         </is>
       </c>
     </row>
@@ -484,12 +499,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.04138</t>
+          <t>$0.04133</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.94%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>$74,179,937</t>
         </is>
       </c>
     </row>
@@ -504,12 +524,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$1.42</t>
+          <t>$1.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>$160,420,045</t>
         </is>
       </c>
     </row>
@@ -524,12 +549,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.9999</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>$182,874,048</t>
         </is>
       </c>
     </row>
@@ -549,7 +579,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>$793,091,315</t>
         </is>
       </c>
     </row>
@@ -569,7 +604,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>$546,482</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,22 +444,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>siren83SIREN</t>
+          <t>siren88SIREN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.6968</t>
+          <t>$0.6378</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48.06%</t>
+          <t>59.54%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$285,903,398</t>
+          <t>$255,520,180</t>
         </is>
       </c>
     </row>
@@ -469,22 +469,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Worldcoin60WLD</t>
+          <t>Worldcoin62WLD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.3011</t>
+          <t>$0.2862</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>9.43%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$217,787,632</t>
+          <t>$255,173,683</t>
         </is>
       </c>
     </row>
@@ -499,17 +499,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.04133</t>
+          <t>$0.04148</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$74,179,937</t>
+          <t>$69,786,630</t>
         </is>
       </c>
     </row>
@@ -519,22 +519,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Toncoin30TON</t>
+          <t>PancakeSwap82CAKE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$1.41</t>
+          <t>$1.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$160,420,045</t>
+          <t>$66,523,897</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Filecoin68FIL</t>
+          <t>Zcash19ZEC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$0.9999</t>
+          <t>$332.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$182,874,048</t>
+          <t>$456,061,631</t>
         </is>
       </c>
     </row>
@@ -569,22 +569,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TRON8TRX</t>
+          <t>Bonk78BONK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$0.3253</t>
+          <t>$0.056534</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$793,091,315</t>
+          <t>$123,593,913</t>
         </is>
       </c>
     </row>
@@ -594,22 +594,222 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Dash87DASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>$37.11</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>$100,221,661</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Toncoin30TON</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>$1.40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>$164,278,856</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LayerZero75ZRO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>$46,213,647</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>UNUS SED LEO12LEO</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>$10.13</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>$546,482</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>$546,009</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Avalanche24AVAX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>$9.78</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>$433,564,827</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>XDC Network74XDC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>$0.03135</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>$24,754,028</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Algorand57ALGO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>$0.1128</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>$65,898,142</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>World Liberty Financial34WLFI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>$0.08222</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>$109,241,378</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pump.fun71PUMP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>$0.00203</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>$92,523,190</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,22 +444,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>siren88SIREN</t>
+          <t>siren83SIREN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.6378</t>
+          <t>$0.6868</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59.54%</t>
+          <t>64.36%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$255,520,180</t>
+          <t>$182,657,209</t>
         </is>
       </c>
     </row>
@@ -474,17 +474,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.2862</t>
+          <t>$0.2832</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>11.38%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$255,173,683</t>
+          <t>$296,720,581</t>
         </is>
       </c>
     </row>
@@ -494,22 +494,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chiliz92CHZ</t>
+          <t>Algorand57ALGO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.04148</t>
+          <t>$0.1112</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$69,786,630</t>
+          <t>$54,036,880</t>
         </is>
       </c>
     </row>
@@ -519,22 +519,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PancakeSwap82CAKE</t>
+          <t>Toncoin30TON</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$1.59</t>
+          <t>$1.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$66,523,897</t>
+          <t>$157,693,802</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zcash19ZEC</t>
+          <t>OFFICIAL TRUMP70TRUMP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$332.22</t>
+          <t>$2.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$456,061,631</t>
+          <t>$181,968,400</t>
         </is>
       </c>
     </row>
@@ -569,22 +569,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bonk78BONK</t>
+          <t>PancakeSwap82CAKE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$0.056534</t>
+          <t>$1.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$123,593,913</t>
+          <t>$62,025,270</t>
         </is>
       </c>
     </row>
@@ -594,22 +594,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dash87DASH</t>
+          <t>Artificial Superintelligence Alliance81FET</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$37.11</t>
+          <t>$0.2285</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$100,221,661</t>
+          <t>$201,435,623</t>
         </is>
       </c>
     </row>
@@ -619,22 +619,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Toncoin30TON</t>
+          <t>XDC Network75XDC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$1.40</t>
+          <t>$0.03091</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$164,278,856</t>
+          <t>$25,930,784</t>
         </is>
       </c>
     </row>
@@ -644,22 +644,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LayerZero75ZRO</t>
+          <t>NEAR Protocol42NEAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$1.96</t>
+          <t>$1.40</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>$46,213,647</t>
+          <t>$271,354,137</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNUS SED LEO12LEO</t>
+          <t>Render59RENDER</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$10.13</t>
+          <t>$1.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>$546,009</t>
+          <t>$106,035,372</t>
         </is>
       </c>
     </row>
@@ -694,22 +694,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Avalanche24AVAX</t>
+          <t>VeChain73VET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$9.78</t>
+          <t>$0.00723</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>$433,564,827</t>
+          <t>$24,048,070</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XDC Network74XDC</t>
+          <t>World Liberty Financial34WLFI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$0.03135</t>
+          <t>$0.0806</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>$24,754,028</t>
+          <t>$104,483,874</t>
         </is>
       </c>
     </row>
@@ -744,22 +744,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Algorand57ALGO</t>
+          <t>Stacks90STX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$0.1128</t>
+          <t>$0.239</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>$65,898,142</t>
+          <t>$20,055,425</t>
         </is>
       </c>
     </row>
@@ -769,22 +769,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>World Liberty Financial34WLFI</t>
+          <t>Bonk80BONK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$0.08222</t>
+          <t>$0.056384</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>$109,241,378</t>
+          <t>$98,350,758</t>
         </is>
       </c>
     </row>
@@ -794,22 +794,122 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pump.fun71PUMP</t>
+          <t>Filecoin68FIL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$0.00203</t>
+          <t>$0.9775</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>$92,523,190</t>
+          <t>$157,523,183</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pepe46PEPE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>$0.053922</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>$625,382,950</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LayerZero74ZRO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>$1.95</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>$42,576,135</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aptos66APT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>$0.9804</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>$104,535,125</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sei97SEI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>$0.0579</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>$44,771,430</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,22 +444,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>siren83SIREN</t>
+          <t>siren81SIREN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.6868</t>
+          <t>$0.7006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64.36%</t>
+          <t>65.66%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$182,657,209</t>
+          <t>$177,523,169</t>
         </is>
       </c>
     </row>
@@ -474,17 +474,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.2832</t>
+          <t>$0.2816</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.38%</t>
+          <t>11.39%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$296,720,581</t>
+          <t>$305,768,614</t>
         </is>
       </c>
     </row>
@@ -499,17 +499,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.1112</t>
+          <t>$0.1107</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$54,036,880</t>
+          <t>$53,919,285</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$157,693,802</t>
+          <t>$156,133,045</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OFFICIAL TRUMP70TRUMP</t>
+          <t>PancakeSwap83CAKE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$2.99</t>
+          <t>$1.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$181,968,400</t>
+          <t>$61,843,569</t>
         </is>
       </c>
     </row>
@@ -569,22 +569,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PancakeSwap82CAKE</t>
+          <t>OFFICIAL TRUMP70TRUMP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$1.57</t>
+          <t>$2.99</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$62,025,270</t>
+          <t>$183,383,858</t>
         </is>
       </c>
     </row>
@@ -594,22 +594,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Artificial Superintelligence Alliance81FET</t>
+          <t>Artificial Superintelligence Alliance82FET</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$0.2285</t>
+          <t>$0.2292</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$201,435,623</t>
+          <t>$199,544,463</t>
         </is>
       </c>
     </row>
@@ -619,22 +619,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XDC Network75XDC</t>
+          <t>Stacks91STX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$0.03091</t>
+          <t>$0.2381</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$25,930,784</t>
+          <t>$20,341,360</t>
         </is>
       </c>
     </row>
@@ -644,22 +644,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NEAR Protocol42NEAR</t>
+          <t>LayerZero76ZRO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$1.40</t>
+          <t>$1.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>$271,354,137</t>
+          <t>$42,483,384</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Render59RENDER</t>
+          <t>XDC Network74XDC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$1.85</t>
+          <t>$0.03109</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>$106,035,372</t>
+          <t>$26,255,450</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$0.00723</t>
+          <t>$0.007236</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>$24,048,070</t>
+          <t>$24,382,797</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>World Liberty Financial34WLFI</t>
+          <t>NEAR Protocol42NEAR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$0.0806</t>
+          <t>$1.40</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>$104,483,874</t>
+          <t>$272,745,339</t>
         </is>
       </c>
     </row>
@@ -744,22 +744,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stacks90STX</t>
+          <t>World Liberty Financial34WLFI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$0.239</t>
+          <t>$0.08064</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>$20,055,425</t>
+          <t>$103,939,325</t>
         </is>
       </c>
     </row>
@@ -769,22 +769,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bonk80BONK</t>
+          <t>Venice Token95VVV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$0.056384</t>
+          <t>$8.93</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>$98,350,758</t>
+          <t>$22,407,761</t>
         </is>
       </c>
     </row>
@@ -794,22 +794,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Filecoin68FIL</t>
+          <t>Render59RENDER</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$0.9775</t>
+          <t>$1.86</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>$157,523,183</t>
+          <t>$106,598,424</t>
         </is>
       </c>
     </row>
@@ -819,97 +819,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pepe46PEPE</t>
+          <t>Filecoin68FIL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$0.053922</t>
+          <t>$0.9781</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>$625,382,950</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LayerZero74ZRO</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>$1.95</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.15%</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>$42,576,135</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Aptos66APT</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>$0.9804</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>$104,535,125</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Sei97SEI</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>$0.0579</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>$44,771,430</t>
+          <t>$158,332,611</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,428 +413,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>24h Change</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>24h Change</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>Volume(24h)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>siren84SIREN</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>siren81SIREN</t>
+          <t>$0.7112</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.7006</t>
+          <t>65.83%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>65.66%</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>$177,523,169</t>
+          <t>$166,076,225</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Worldcoin61WLD</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Worldcoin62WLD</t>
+          <t>$0.2872</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.2816</t>
+          <t>9.87%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.39%</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>$305,768,614</t>
+          <t>$308,351,768</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Algorand57ALGO</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Algorand57ALGO</t>
+          <t>$0.1116</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.1107</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.39%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>$53,919,285</t>
+          <t>$53,182,799</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Toncoin30TON</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Toncoin30TON</t>
+          <t>$1.40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$1.40</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.03%</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>$156,133,045</t>
+          <t>$151,353,430</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PancakeSwap83CAKE</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PancakeSwap83CAKE</t>
+          <t>$1.59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$1.58</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>$61,843,569</t>
+          <t>$61,753,770</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UNUS SED LEO11LEO</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OFFICIAL TRUMP70TRUMP</t>
+          <t>$10.14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$2.99</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44%</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>$183,383,858</t>
+          <t>$524,198</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Canton20CC</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Artificial Superintelligence Alliance82FET</t>
+          <t>$0.1486</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$0.2292</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.01%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>$199,544,463</t>
+          <t>$12,642,674</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEAR Protocol42NEAR</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stacks91STX</t>
+          <t>$1.42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$0.2381</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>$20,341,360</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LayerZero76ZRO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>$1.94</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.70%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>$42,483,384</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>XDC Network74XDC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>$0.03109</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.67%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>$26,255,450</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>VeChain73VET</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>$0.007236</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>$24,382,797</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NEAR Protocol42NEAR</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>$1.40</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>$272,745,339</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>World Liberty Financial34WLFI</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>$0.08064</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>$103,939,325</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Venice Token95VVV</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>$8.93</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.34%</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>$22,407,761</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Render59RENDER</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>$1.86</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>$106,598,424</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Filecoin68FIL</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>$0.9781</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>$158,332,611</t>
+          <t>$272,469,032</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,176 +441,660 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>siren84SIREN</t>
+          <t>Hyperliquid10HYPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$0.7112</t>
+          <t>$40.86</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.83%</t>
+          <t>5.71%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$166,076,225</t>
+          <t>$346,377,139</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Worldcoin61WLD</t>
+          <t>Mantle38MNT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$0.2872</t>
+          <t>$0.6221</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$308,351,768</t>
+          <t>$1,741,292,640</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Algorand57ALGO</t>
+          <t>Monad97MON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$0.1116</t>
+          <t>$0.03064</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>4.60%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$53,182,799</t>
+          <t>$88,575,583</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Toncoin30TON</t>
+          <t>Zcash20ZEC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$1.40</t>
+          <t>$309.80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$151,353,430</t>
+          <t>$632,371,164</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PancakeSwap83CAKE</t>
+          <t>Jupiter72JUP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$1.59</t>
+          <t>$0.1701</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$61,753,770</t>
+          <t>$24,386,906</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UNUS SED LEO11LEO</t>
+          <t>ether.fi96ETHFI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$10.14</t>
+          <t>$0.4567</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$524,198</t>
+          <t>$25,948,171</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Canton20CC</t>
+          <t>Celestia98TIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$0.1486</t>
+          <t>$0.385</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$12,642,674</t>
+          <t>$52,558,916</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEAR Protocol42NEAR</t>
+          <t>Artificial Superintelligence Alliance84FET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$1.42</t>
+          <t>$0.2076</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$272,469,032</t>
+          <t>$144,037,395</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Midnight75NIGHT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>$0.03574</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>$21,837,352</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LayerZero81ZRO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>$1.57</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>$128,746,729</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ethena55ENA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>$0.1147</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.51%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>$130,901,619</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sun [New]100SUN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>$0.01807</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>$72,043,125</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Algorand59ALGO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>$0.1025</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>$32,664,774</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stacks93STX</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>$0.2222</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>$10,435,851</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Flare68FLR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>$0.007973</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>$2,951,514</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TRON8TRX</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>$0.3297</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>$1,055,424,224</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Nexo77NEXO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$0.8808</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>$9,373,104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Internet Computer48ICP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$2.43</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>$47,025,524</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pump.fun73PUMP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$0.001806</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>$45,610,092</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>World Liberty Financial33WLFI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$0.07737</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>$55,225,132</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>XRP4XRP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$1.41</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>$3,033,461,168</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OKB41OKB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>$82.87</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>$25,063,253</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ethereum2ETH</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$2,295.16</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>$17,956,884,533</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ondo52ONDO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>$0.252</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>$93,550,505</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PancakeSwap76CAKE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>$1.52</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>$32,453,012</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kaspa57KAS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>$0.03412</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>$25,566,401</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Morpho64MORPHO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>$27,853,819</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bitcoin1BTC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>$74,754.47</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>$34,666,601,494</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VeChain71VET</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>$0.007035</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>$23,480,694</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Litecoin23LTC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>$54.82</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>$227,121,450</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,660 +441,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hyperliquid10HYPE</t>
+          <t>Ethena56ENA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$40.86</t>
+          <t>$0.111</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$346,377,139</t>
+          <t>$105,208,608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mantle38MNT</t>
+          <t>DeXe52DEXE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$0.6221</t>
+          <t>$14.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$1,741,292,640</t>
+          <t>$34,444,895</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Monad97MON</t>
+          <t>Morpho64MORPHO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$0.03064</t>
+          <t>$1.90</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.60%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$88,575,583</t>
+          <t>$14,061,153</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Zcash20ZEC</t>
+          <t>ether.fi97ETHFI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$309.80</t>
+          <t>$0.4533</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$632,371,164</t>
+          <t>$26,036,870</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jupiter72JUP</t>
+          <t>TRON8TRX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$0.1701</t>
+          <t>$0.3288</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$24,386,906</t>
+          <t>$779,915,266</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ether.fi96ETHFI</t>
+          <t>Pi42PI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$0.4567</t>
+          <t>$0.1702</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$25,948,171</t>
+          <t>$21,329,138</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Celestia98TIA</t>
+          <t>Midnight73NIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$0.385</t>
+          <t>$0.0362</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$52,558,916</t>
+          <t>$21,716,077</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Artificial Superintelligence Alliance84FET</t>
+          <t>Jupiter74JUP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$0.2076</t>
+          <t>$0.1682</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$144,037,395</t>
+          <t>$21,067,390</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Midnight75NIGHT</t>
+          <t>Uniswap38UNI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$0.03574</t>
+          <t>$3.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$21,837,352</t>
+          <t>$222,471,669</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LayerZero81ZRO</t>
+          <t>siren80SIREN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$1.57</t>
+          <t>$0.714</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$128,746,729</t>
+          <t>$17,078,832</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ethena55ENA</t>
+          <t>Aster43ASTER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$0.1147</t>
+          <t>$0.6786</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>$130,901,619</t>
+          <t>$125,977,719</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sun [New]100SUN</t>
+          <t>Hyperliquid10HYPE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$0.01807</t>
+          <t>$41.28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>$72,043,125</t>
+          <t>$334,006,302</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Algorand59ALGO</t>
+          <t>Sun [New]100SUN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$0.1025</t>
+          <t>$0.0182</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>$32,664,774</t>
+          <t>$71,821,618</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stacks93STX</t>
+          <t>Filecoin67FIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$0.2222</t>
+          <t>$0.9222</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>$10,435,851</t>
+          <t>$98,265,905</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Flare68FLR</t>
+          <t>NEAR Protocol41NEAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$0.007973</t>
+          <t>$1.36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>$2,951,514</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TRON8TRX</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>$0.3297</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>$1,055,424,224</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Nexo77NEXO</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>$0.8808</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1.25%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>$9,373,104</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Internet Computer48ICP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>$2.43</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1.23%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>$47,025,524</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pump.fun73PUMP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>$0.001806</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1.22%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>$45,610,092</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>World Liberty Financial33WLFI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>$0.07737</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.20%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>$55,225,132</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>XRP4XRP</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>$1.41</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1.19%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>$3,033,461,168</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>OKB41OKB</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>$82.87</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1.07%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>$25,063,253</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Ethereum2ETH</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>$2,295.16</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>$17,956,884,533</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Ondo52ONDO</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>$0.252</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>$93,550,505</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PancakeSwap76CAKE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>$1.52</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.93%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>$32,453,012</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Kaspa57KAS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>$0.03412</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>$25,566,401</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Morpho64MORPHO</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>$1.96</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>$27,853,819</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Bitcoin1BTC</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>$74,754.47</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0.68%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>$34,666,601,494</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>VeChain71VET</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>$0.007035</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0.67%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>$23,480,694</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Litecoin23LTC</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>$54.82</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>$227,121,450</t>
+          <t>$182,563,946</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$0.111</t>
+          <t>$0.1115</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.16%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$105,208,608</t>
+          <t>$99,396,444</t>
         </is>
       </c>
     </row>
@@ -468,303 +468,171 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$14.33</t>
+          <t>$14.35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$34,444,895</t>
+          <t>$30,964,889</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Morpho64MORPHO</t>
+          <t>Pi42PI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$1.90</t>
+          <t>$0.1701</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$14,061,153</t>
+          <t>$22,966,977</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ether.fi97ETHFI</t>
+          <t>Uniswap38UNI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$0.4533</t>
+          <t>$3.26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$26,036,870</t>
+          <t>$220,583,101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRON8TRX</t>
+          <t>Canton17CC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$0.3288</t>
+          <t>$0.1507</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$779,915,266</t>
+          <t>$26,167,425</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pi42PI</t>
+          <t>TRON8TRX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$0.1702</t>
+          <t>$0.3291</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$21,329,138</t>
+          <t>$730,877,619</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Midnight73NIGHT</t>
+          <t>ether.fi98ETHFI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$0.0362</t>
+          <t>$0.4562</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$21,716,077</t>
+          <t>$25,400,736</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jupiter74JUP</t>
+          <t>Jupiter75JUP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$0.1682</t>
+          <t>$0.1699</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$21,067,390</t>
+          <t>$19,985,605</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uniswap38UNI</t>
+          <t>PAX Gold34PAXG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$3.24</t>
+          <t>$4,776.42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$222,471,669</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>siren80SIREN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>$0.714</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.91%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>$17,078,832</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Aster43ASTER</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>$0.6786</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>$125,977,719</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Hyperliquid10HYPE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>$41.28</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>$334,006,302</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sun [New]100SUN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>$0.0182</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>$71,821,618</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Filecoin67FIL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>$0.9222</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>$98,265,905</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEAR Protocol41NEAR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>$1.36</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>$182,563,946</t>
+          <t>$231,573,504</t>
         </is>
       </c>
     </row>

--- a/losers.xlsx
+++ b/losers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,44 +441,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ethena56ENA</t>
+          <t>DeXe53DEXE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$0.1115</t>
+          <t>$12.56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>10.69%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$99,396,444</t>
+          <t>$36,036,307</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DeXe52DEXE</t>
+          <t>Hyperliquid10HYPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$14.35</t>
+          <t>$39.83</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$30,964,889</t>
+          <t>$350,687,873</t>
         </is>
       </c>
     </row>
@@ -490,149 +490,611 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$0.1701</t>
+          <t>$0.1678</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$22,966,977</t>
+          <t>$24,045,625</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uniswap38UNI</t>
+          <t>Ethena56ENA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$3.26</t>
+          <t>$0.1111</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$220,583,101</t>
+          <t>$101,641,819</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canton17CC</t>
+          <t>ether.fi97ETHFI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$0.1507</t>
+          <t>$0.4479</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$26,167,425</t>
+          <t>$23,498,324</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRON8TRX</t>
+          <t>Arbitrum65ARB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$0.3291</t>
+          <t>$0.1253</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$730,877,619</t>
+          <t>$73,778,239</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ether.fi98ETHFI</t>
+          <t>Quant61QNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$0.4562</t>
+          <t>$72.79</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$25,400,736</t>
+          <t>$8,741,400</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jupiter75JUP</t>
+          <t>Canton17CC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$0.1699</t>
+          <t>$0.152</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$19,985,605</t>
+          <t>$28,301,899</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAX Gold34PAXG</t>
+          <t>Tether Gold32XAUt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$4,776.42</t>
+          <t>$4,697.39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$231,573,504</t>
+          <t>$180,867,525</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PAX Gold35PAXG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>$4,699.77</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>$213,111,981</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Artificial Superintelligence Alliance86FET</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>$0.2081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>$137,019,640</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Virtuals Protocol89VIRTUAL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>$0.679</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.77%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>$67,513,375</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stacks93STX</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>$0.2216</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.64%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>$6,819,054</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sky39SKY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>$0.07869</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>$16,311,489</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aerodrome Finance100AERO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>$0.3798</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>$15,521,316</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bittensor31TAO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>$243.82</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>$178,302,241</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KuCoin Token52KCS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>$12,139,107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Polygon (prev. MATIC)55POL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$0.09325</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>$58,404,842</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>XDC Network75XDC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$0.02994</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>$21,618,517</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aptos66APT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$0.9289</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>$53,899,144</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mantle37MNT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$0.6313</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>$840,097,433</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OFFICIAL TRUMP70TRUMP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>$2.84</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>$192,770,375</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tezos94XTZ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$0.3637</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>$11,765,408</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Worldcoin62WLD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>$0.2619</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>$117,145,133</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kaspa57KAS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>$0.03464</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>$20,531,754</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Jupiter74JUP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>$0.1693</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>$20,433,581</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Aster43ASTER</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>$0.674</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>$128,923,872</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>siren80SIREN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>$0.6951</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>$15,995,715</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VeChain72VET</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>$0.007079</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>$19,701,976</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sui27SUI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>$0.9363</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>$355,797,175</t>
         </is>
       </c>
     </row>
